--- a/INVENTORY_REPORT_2026_v2.xlsx
+++ b/INVENTORY_REPORT_2026_v2.xlsx
@@ -22764,7 +22764,7 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAMSUNG S21+ 128GB </t>
+          <t>Samsung Galaxy S21 Plus 5G 128GB</t>
         </is>
       </c>
       <c r="C227" s="26" t="n">
